--- a/data/trans_dic/P1427-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P1427-Edad-trans_dic.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,32%</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,04</t>
+          <t>0,0; 0,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -703,12 +703,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,47</t>
+          <t>0,0; 3,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,53</t>
+          <t>0,0; 0,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,8</t>
+          <t>0,0; 1,81</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
     </row>
@@ -798,17 +798,17 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,69</t>
+          <t>0,0; 2,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,81</t>
+          <t>0,0; 0,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,09</t>
+          <t>0,0; 0,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,41</t>
+          <t>0,0; 0,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,23</t>
+          <t>0,0; 1,51</t>
         </is>
       </c>
     </row>
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,19%</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,48</t>
+          <t>0,15; 1,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -913,32 +913,32 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,41</t>
+          <t>0,0; 1,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,8</t>
+          <t>0,0; 0,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,11</t>
+          <t>0,12; 1,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,13</t>
+          <t>0,21; 1,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,52</t>
+          <t>0,0; 0,47</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,63</t>
+          <t>0,0; 0,5</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,58</t>
+          <t>0,0; 2,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1018,37 +1018,37 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,77</t>
+          <t>0,44; 2,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,38</t>
+          <t>0,16; 1,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,46</t>
+          <t>0,15; 1,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 4,2</t>
+          <t>0,69; 2,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,21</t>
+          <t>0,16; 1,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,66</t>
+          <t>0,08; 0,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,62</t>
+          <t>0,68; 1,71</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,2; 4,11</t>
+          <t>0,98; 4,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,76</t>
+          <t>0,2; 1,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,95; 4,61</t>
+          <t>1,83; 4,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,88; 5,22</t>
+          <t>1,74; 5,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,19; 4,22</t>
+          <t>1,1; 4,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,12; 4,29</t>
+          <t>2,09; 4,35</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,87</t>
+          <t>1,73; 3,94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,5</t>
+          <t>0,86; 2,52</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,19; 3,89</t>
+          <t>2,34; 3,99</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,71; 10,71</t>
+          <t>4,56; 10,84</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,28; 6,72</t>
+          <t>2,17; 6,45</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,18; 10,53</t>
+          <t>5,72; 9,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,46; 10,39</t>
+          <t>4,63; 10,39</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,87; 8,76</t>
+          <t>4,05; 9,27</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,49; 10,36</t>
+          <t>8,2; 12,24</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,25; 9,27</t>
+          <t>5,34; 9,2</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,5; 6,86</t>
+          <t>3,57; 7,04</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,37; 9,45</t>
+          <t>7,34; 10,56</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,19%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,66; 16,52</t>
+          <t>7,19; 16,49</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,76; 10,69</t>
+          <t>4,74; 10,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,84; 20,64</t>
+          <t>13,54; 20,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,41; 16,1</t>
+          <t>9,38; 16,25</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,15; 13,95</t>
+          <t>7,04; 13,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,17; 22,66</t>
+          <t>16,86; 22,28</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,53; 15,08</t>
+          <t>9,41; 14,93</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,0; 11,51</t>
+          <t>6,95; 11,41</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16,59; 20,87</t>
+          <t>16,34; 20,2</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,56; 2,51</t>
+          <t>1,54; 2,58</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,74; 1,42</t>
+          <t>0,75; 1,41</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,34; 3,64</t>
+          <t>2,61; 3,63</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,13; 3,28</t>
+          <t>2,14; 3,31</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,79; 2,81</t>
+          <t>1,78; 2,83</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,41; 4,97</t>
+          <t>3,93; 4,99</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,95; 2,7</t>
+          <t>1,95; 2,69</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,35; 2,01</t>
+          <t>1,39; 2,03</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,18; 4,14</t>
+          <t>3,46; 4,19</t>
         </is>
       </c>
     </row>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2562</t>
+          <t>2464</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2562</t>
+          <t>2464</t>
         </is>
       </c>
     </row>
@@ -1750,7 +1750,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4735</t>
+          <t>0; 4187</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 17132</t>
+          <t>0; 12528</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4688</t>
+          <t>0; 4373</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 12812</t>
+          <t>0; 13930</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2260</t>
+          <t>2433</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2260</t>
+          <t>2433</t>
         </is>
       </c>
     </row>
@@ -1923,17 +1923,17 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 11413</t>
+          <t>0; 13978</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4963</t>
+          <t>0; 5260</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 6125</t>
+          <t>0; 4962</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1943,17 +1943,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 5285</t>
+          <t>0; 6267</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 5899</t>
+          <t>0; 5922</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 11486</t>
+          <t>0; 14766</t>
         </is>
       </c>
     </row>
@@ -2048,7 +2048,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2234</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2234</t>
+          <t>2354</t>
         </is>
       </c>
     </row>
@@ -2076,7 +2076,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1044; 10109</t>
+          <t>1056; 10231</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2091,32 +2091,32 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 10022</t>
+          <t>0; 12461</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5317</t>
+          <t>0; 6193</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>727; 5990</t>
+          <t>751; 6334</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2858; 15706</t>
+          <t>2964; 15011</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 6909</t>
+          <t>0; 6234</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>728; 6773</t>
+          <t>0; 6192</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7688</t>
+          <t>7699</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12487</t>
+          <t>8658</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>20175</t>
+          <t>16358</t>
         </is>
       </c>
     </row>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 9696</t>
+          <t>0; 13138</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2249,37 +2249,37 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2311; 15673</t>
+          <t>3080; 14339</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>959; 8500</t>
+          <t>966; 9216</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1000; 9471</t>
+          <t>995; 8455</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5284; 29895</t>
+          <t>5076; 14844</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2055; 14842</t>
+          <t>1940; 15532</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>997; 8581</t>
+          <t>1000; 8729</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10732; 41962</t>
+          <t>9836; 24525</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17026</t>
+          <t>17274</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16587</t>
+          <t>19087</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>33613</t>
+          <t>36361</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5157; 17669</t>
+          <t>4207; 17524</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>964; 8422</t>
+          <t>961; 8540</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10909; 25824</t>
+          <t>11152; 26857</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8429; 23393</t>
+          <t>7801; 23189</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5921; 20976</t>
+          <t>5463; 21055</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11527; 23310</t>
+          <t>12678; 26333</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13964; 33981</t>
+          <t>15218; 34522</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7849; 24418</t>
+          <t>8402; 24594</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>24180; 42900</t>
+          <t>28376; 48511</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>29774</t>
+          <t>31042</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>39161</t>
+          <t>43288</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>68935</t>
+          <t>74330</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>14603; 33176</t>
+          <t>14120; 33577</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7625; 22469</t>
+          <t>7264; 21564</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>22659; 38630</t>
+          <t>23180; 40268</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>15802; 36784</t>
+          <t>16391; 36791</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>14608; 33074</t>
+          <t>15294; 35019</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15150; 62974</t>
+          <t>35958; 53686</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34816; 61539</t>
+          <t>35469; 61057</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>24956; 48842</t>
+          <t>25396; 50115</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>32812; 92083</t>
+          <t>61993; 89134</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>48697</t>
+          <t>51171</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>83761</t>
+          <t>89577</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>132458</t>
+          <t>140748</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>19151; 41279</t>
+          <t>17971; 41211</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>12222; 27469</t>
+          <t>12188; 27547</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>39015; 58185</t>
+          <t>41878; 62474</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>36585; 62632</t>
+          <t>36476; 63201</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>28603; 55818</t>
+          <t>28172; 54778</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>73135; 96506</t>
+          <t>78322; 103506</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>60897; 96335</t>
+          <t>60121; 95379</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>45976; 75627</t>
+          <t>45679; 74997</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>117381; 147724</t>
+          <t>126437; 156286</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>105444</t>
+          <t>109619</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>156792</t>
+          <t>165427</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>262236</t>
+          <t>275046</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>53484; 86156</t>
+          <t>52928; 88371</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>25073; 48345</t>
+          <t>25492; 48016</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>80934; 125683</t>
+          <t>92165; 128153</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>75593; 116739</t>
+          <t>76098; 117673</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>63420; 99565</t>
+          <t>63030; 100160</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>124658; 181666</t>
+          <t>146671; 186357</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>136186; 188561</t>
+          <t>136074; 187911</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>93876; 139477</t>
+          <t>96676; 141206</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>226231; 294663</t>
+          <t>250908; 304092</t>
         </is>
       </c>
     </row>
